--- a/PCB/PickAndPlace.xlsx
+++ b/PCB/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB_2026-04-10" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB2_2026-04-13" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="377">
   <si>
     <t>Designator</t>
   </si>
@@ -181,901 +181,967 @@
     <t>-77.594mm</t>
   </si>
   <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>25121WJ0471T4E</t>
-  </si>
-  <si>
-    <t>R2512</t>
-  </si>
-  <si>
-    <t>52.155mm</t>
-  </si>
-  <si>
-    <t>-22.919mm</t>
-  </si>
-  <si>
-    <t>49.089mm</t>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>MB6S-50MIL</t>
+  </si>
+  <si>
+    <t>MBS_L4.7-W3.8-P2.40-LS7.0-TL</t>
+  </si>
+  <si>
+    <t>58.928mm</t>
+  </si>
+  <si>
+    <t>-84.709mm</t>
+  </si>
+  <si>
+    <t>55.828mm</t>
+  </si>
+  <si>
+    <t>-83.509mm</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>EL817S1(B)(TU)-F</t>
+  </si>
+  <si>
+    <t>SOP-4_L6.5-W4.6-P2.54-LS10.2-TL</t>
+  </si>
+  <si>
+    <t>44.831mm</t>
+  </si>
+  <si>
+    <t>-84.836mm</t>
+  </si>
+  <si>
+    <t>49.931mm</t>
+  </si>
+  <si>
+    <t>-86.106mm</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>1206W4J0102T5E_C1469</t>
+  </si>
+  <si>
+    <t>R1206</t>
+  </si>
+  <si>
+    <t>38.862mm</t>
+  </si>
+  <si>
+    <t>-79.375mm</t>
+  </si>
+  <si>
+    <t>-77.896mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CL10C200JB8NNNC</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>8.128mm</t>
+  </si>
+  <si>
+    <t>-31.75mm</t>
+  </si>
+  <si>
+    <t>7.633mm</t>
+  </si>
+  <si>
+    <t>-32.245mm</t>
+  </si>
+  <si>
+    <t>20pF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>7.366mm</t>
+  </si>
+  <si>
+    <t>-42.418mm</t>
+  </si>
+  <si>
+    <t>6.871mm</t>
+  </si>
+  <si>
+    <t>-41.923mm</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>5.969mm</t>
+  </si>
+  <si>
+    <t>-56.388mm</t>
+  </si>
+  <si>
+    <t>-50.038mm</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>1206W4F1004T5E</t>
+  </si>
+  <si>
+    <t>7.112mm</t>
+  </si>
+  <si>
+    <t>-36.957mm</t>
+  </si>
+  <si>
+    <t>-38.436mm</t>
+  </si>
+  <si>
+    <t>1MΩ</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6</t>
+  </si>
+  <si>
+    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
+  </si>
+  <si>
+    <t>16.383mm</t>
+  </si>
+  <si>
+    <t>-38.354mm</t>
+  </si>
+  <si>
+    <t>12.133mm</t>
+  </si>
+  <si>
+    <t>-35.604mm</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>X49SM8MSD2SC</t>
+  </si>
+  <si>
+    <t>CRYSTAL-SMD_L11.5-W4.8-LS12.7</t>
+  </si>
+  <si>
+    <t>3.175mm</t>
+  </si>
+  <si>
+    <t>-42.804mm</t>
+  </si>
+  <si>
+    <t>8MHz</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>HLK-5M03</t>
+  </si>
+  <si>
+    <t>PWRM-TH_HLK-5M03</t>
+  </si>
+  <si>
+    <t>25.019mm</t>
+  </si>
+  <si>
+    <t>-80.645mm</t>
+  </si>
+  <si>
+    <t>22.019mm</t>
+  </si>
+  <si>
+    <t>-97.445mm</t>
+  </si>
+  <si>
+    <t>H6</t>
+  </si>
+  <si>
+    <t>17.399mm</t>
+  </si>
+  <si>
+    <t>-15.875mm</t>
+  </si>
+  <si>
+    <t>11.049mm</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>11.811mm</t>
+  </si>
+  <si>
+    <t>-24.384mm</t>
+  </si>
+  <si>
+    <t>13.29mm</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>13.081mm</t>
+  </si>
+  <si>
+    <t>-29.845mm</t>
+  </si>
+  <si>
+    <t>14.56mm</t>
+  </si>
+  <si>
+    <t>p8</t>
+  </si>
+  <si>
+    <t>2.54-1*1P针</t>
+  </si>
+  <si>
+    <t>HDR-TH_1P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>5.842mm</t>
+  </si>
+  <si>
+    <t>-66.392mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>0402F104M500NT</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>13.589mm</t>
+  </si>
+  <si>
+    <t>-32.385mm</t>
+  </si>
+  <si>
+    <t>13.169mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>21.844mm</t>
+  </si>
+  <si>
+    <t>-35.306mm</t>
+  </si>
+  <si>
+    <t>21.424mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>19.072mm</t>
+  </si>
+  <si>
+    <t>-43.982mm</t>
+  </si>
+  <si>
+    <t>19.492mm</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>9.525mm</t>
+  </si>
+  <si>
+    <t>-39.624mm</t>
+  </si>
+  <si>
+    <t>9.228mm</t>
+  </si>
+  <si>
+    <t>-39.327mm</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>8.255mm</t>
+  </si>
+  <si>
+    <t>-64.643mm</t>
+  </si>
+  <si>
+    <t>-65.063mm</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>CL10A106MQ8NNNC</t>
+  </si>
+  <si>
+    <t>21.082mm</t>
+  </si>
+  <si>
+    <t>-44.958mm</t>
+  </si>
+  <si>
+    <t>-44.258mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>RVT1E101M0607</t>
+  </si>
+  <si>
+    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.2-R-RD</t>
+  </si>
+  <si>
+    <t>5.207mm</t>
+  </si>
+  <si>
+    <t>-72.771mm</t>
+  </si>
+  <si>
+    <t>2.652mm</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>DS1021-1x2SF11-B</t>
+  </si>
+  <si>
+    <t>HDR-TH_2P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>11.142mm</t>
+  </si>
+  <si>
+    <t>-64.955mm</t>
+  </si>
+  <si>
+    <t>-63.685mm</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>23.749mm</t>
+  </si>
+  <si>
+    <t>-58.547mm</t>
+  </si>
+  <si>
+    <t>22.479mm</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>12.294mm</t>
+  </si>
+  <si>
+    <t>-13.281mm</t>
+  </si>
+  <si>
+    <t>11.024mm</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>4.1mm</t>
+  </si>
+  <si>
+    <t>-28.479mm</t>
+  </si>
+  <si>
+    <t>3.68mm</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>0805W8J0103T5E</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>3.937mm</t>
+  </si>
+  <si>
+    <t>-16.764mm</t>
+  </si>
+  <si>
+    <t>-15.764mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>4*4*1.7 贴片</t>
+  </si>
+  <si>
+    <t>SW-SMD_4P-L5.2-W5.2-P3.70-LS6.5</t>
+  </si>
+  <si>
+    <t>4.191mm</t>
+  </si>
+  <si>
+    <t>-23.368mm</t>
+  </si>
+  <si>
+    <t>6.041mm</t>
+  </si>
+  <si>
+    <t>-20.268mm</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>S6125-M2-0.5A</t>
+  </si>
+  <si>
+    <t>FUSE-SMD_L6.1-W2.5</t>
+  </si>
+  <si>
+    <t>88.9mm</t>
+  </si>
+  <si>
+    <t>-73.152mm</t>
+  </si>
+  <si>
+    <t>87.132mm</t>
+  </si>
+  <si>
+    <t>-71.384mm</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>10D471K_C8760</t>
+  </si>
+  <si>
+    <t>RES-TH_L12.5-W6.7-P7.50-D1.2</t>
+  </si>
+  <si>
+    <t>86.995mm</t>
+  </si>
+  <si>
+    <t>-82.423mm</t>
+  </si>
+  <si>
+    <t>83.374mm</t>
+  </si>
+  <si>
+    <t>-81.453mm</t>
+  </si>
+  <si>
+    <t>190pF@1kHz</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>CBG321609U600T</t>
+  </si>
+  <si>
+    <t>L1206</t>
+  </si>
+  <si>
+    <t>22.86mm</t>
+  </si>
+  <si>
+    <t>-53.721mm</t>
+  </si>
+  <si>
+    <t>23.986mm</t>
+  </si>
+  <si>
+    <t>-52.595mm</t>
+  </si>
+  <si>
+    <t>zdc</t>
+  </si>
+  <si>
+    <t>29.591mm</t>
+  </si>
+  <si>
+    <t>-53.975mm</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>WJ124-3.81-04P-14-00A</t>
+  </si>
+  <si>
+    <t>CONN-TH_4P-P3.81_KF124-3.81-4P</t>
+  </si>
+  <si>
+    <t>93.599mm</t>
+  </si>
+  <si>
+    <t>-20.955mm</t>
+  </si>
+  <si>
+    <t>-15.24mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>KT-0603Y</t>
+  </si>
+  <si>
+    <t>LED0603-R-RD</t>
+  </si>
+  <si>
+    <t>29.905mm</t>
+  </si>
+  <si>
+    <t>-31.518mm</t>
+  </si>
+  <si>
+    <t>29.154mm</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>-28.347mm</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>-25.176mm</t>
+  </si>
+  <si>
+    <t>LED4</t>
+  </si>
+  <si>
+    <t>-22.005mm</t>
+  </si>
+  <si>
+    <t>LED5</t>
+  </si>
+  <si>
+    <t>-18.834mm</t>
+  </si>
+  <si>
+    <t>R35</t>
+  </si>
+  <si>
+    <t>0402WGF1401TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>27.322mm</t>
+  </si>
+  <si>
+    <t>-18.961mm</t>
+  </si>
+  <si>
+    <t>27.755mm</t>
+  </si>
+  <si>
+    <t>1.4kΩ</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>-22.134mm</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>27.449mm</t>
+  </si>
+  <si>
+    <t>-25.308mm</t>
+  </si>
+  <si>
+    <t>27.882mm</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>27.195mm</t>
+  </si>
+  <si>
+    <t>-28.355mm</t>
+  </si>
+  <si>
+    <t>27.628mm</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>-31.528mm</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>0805W8F2200T5E</t>
+  </si>
+  <si>
+    <t>36.14mm</t>
+  </si>
+  <si>
+    <t>-11.378mm</t>
+  </si>
+  <si>
+    <t>35.14mm</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>36.013mm</t>
+  </si>
+  <si>
+    <t>-25.168mm</t>
+  </si>
+  <si>
+    <t>35.013mm</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
+    <t>-39.084mm</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>36.267mm</t>
+  </si>
+  <si>
+    <t>-53.509mm</t>
+  </si>
+  <si>
+    <t>35.267mm</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>38.354mm</t>
+  </si>
+  <si>
+    <t>-65.405mm</t>
+  </si>
+  <si>
+    <t>-64.405mm</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>1210W2F4702T5E</t>
+  </si>
+  <si>
+    <t>R1210</t>
+  </si>
+  <si>
+    <t>66.167mm</t>
+  </si>
+  <si>
+    <t>-84.455mm</t>
+  </si>
+  <si>
+    <t>65.148mm</t>
+  </si>
+  <si>
+    <t>-83.436mm</t>
+  </si>
+  <si>
+    <t>47kΩ</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>KNP03SJ0100A10</t>
+  </si>
+  <si>
+    <t>RES-TH_BD5.0-L15.5-P19.50-D0.7</t>
+  </si>
+  <si>
+    <t>79.121mm</t>
+  </si>
+  <si>
+    <t>-91.821mm</t>
+  </si>
+  <si>
+    <t>69.703mm</t>
+  </si>
+  <si>
+    <t>-94.344mm</t>
+  </si>
+  <si>
+    <t>10Ω</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>61.468mm</t>
+  </si>
+  <si>
+    <t>-89.154mm</t>
+  </si>
+  <si>
+    <t>62.909mm</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>MMB02070C4700FB200</t>
+  </si>
+  <si>
+    <t>R0207</t>
+  </si>
+  <si>
+    <t>52.07mm</t>
+  </si>
+  <si>
+    <t>-20.32mm</t>
+  </si>
+  <si>
+    <t>49.62mm</t>
   </si>
   <si>
     <t>470Ω</t>
   </si>
   <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>51.901mm</t>
-  </si>
-  <si>
-    <t>-51.103mm</t>
-  </si>
-  <si>
-    <t>48.835mm</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>52.536mm</t>
-  </si>
-  <si>
-    <t>-36.894mm</t>
-  </si>
-  <si>
-    <t>49.47mm</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>52.282mm</t>
-  </si>
-  <si>
-    <t>-79.549mm</t>
-  </si>
-  <si>
-    <t>49.216mm</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>-65.84mm</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>MB6S-50MIL</t>
-  </si>
-  <si>
-    <t>MBS_L4.7-W3.8-P2.40-LS7.0-TL</t>
-  </si>
-  <si>
-    <t>58.928mm</t>
-  </si>
-  <si>
-    <t>-84.709mm</t>
-  </si>
-  <si>
-    <t>55.828mm</t>
-  </si>
-  <si>
-    <t>-83.509mm</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>EL817S1(B)(TU)-F</t>
-  </si>
-  <si>
-    <t>SOP-4_L6.5-W4.6-P2.54-LS10.2-TL</t>
-  </si>
-  <si>
-    <t>44.831mm</t>
-  </si>
-  <si>
-    <t>-84.836mm</t>
-  </si>
-  <si>
-    <t>49.931mm</t>
-  </si>
-  <si>
-    <t>-86.106mm</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>1206W4J0102T5E_C1469</t>
-  </si>
-  <si>
-    <t>R1206</t>
-  </si>
-  <si>
-    <t>37.973mm</t>
-  </si>
-  <si>
-    <t>-75.692mm</t>
-  </si>
-  <si>
-    <t>-74.213mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CL10C200JB8NNNC</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>8.128mm</t>
-  </si>
-  <si>
-    <t>-31.75mm</t>
-  </si>
-  <si>
-    <t>7.633mm</t>
-  </si>
-  <si>
-    <t>-32.245mm</t>
-  </si>
-  <si>
-    <t>20pF</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>7.366mm</t>
-  </si>
-  <si>
-    <t>-42.418mm</t>
-  </si>
-  <si>
-    <t>6.871mm</t>
-  </si>
-  <si>
-    <t>-41.923mm</t>
-  </si>
-  <si>
-    <t>H4</t>
-  </si>
-  <si>
-    <t>5.969mm</t>
-  </si>
-  <si>
-    <t>-56.388mm</t>
-  </si>
-  <si>
-    <t>-50.038mm</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>1206W4F1004T5E</t>
-  </si>
-  <si>
-    <t>7.112mm</t>
-  </si>
-  <si>
-    <t>-36.957mm</t>
-  </si>
-  <si>
-    <t>-38.436mm</t>
-  </si>
-  <si>
-    <t>1MΩ</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>STM32F103C8T6</t>
-  </si>
-  <si>
-    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
-  </si>
-  <si>
-    <t>16.383mm</t>
-  </si>
-  <si>
-    <t>-38.354mm</t>
-  </si>
-  <si>
-    <t>12.133mm</t>
-  </si>
-  <si>
-    <t>-35.604mm</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>X49SM8MSD2SC</t>
-  </si>
-  <si>
-    <t>CRYSTAL-SMD_L11.5-W4.8-LS12.7</t>
-  </si>
-  <si>
-    <t>3.175mm</t>
-  </si>
-  <si>
-    <t>-42.804mm</t>
-  </si>
-  <si>
-    <t>8MHz</t>
-  </si>
-  <si>
-    <t>U13</t>
-  </si>
-  <si>
-    <t>HLK-5M03</t>
-  </si>
-  <si>
-    <t>PWRM-TH_HLK-5M03</t>
-  </si>
-  <si>
-    <t>25.019mm</t>
-  </si>
-  <si>
-    <t>-80.645mm</t>
-  </si>
-  <si>
-    <t>22.019mm</t>
-  </si>
-  <si>
-    <t>-97.445mm</t>
-  </si>
-  <si>
-    <t>H6</t>
-  </si>
-  <si>
-    <t>17.399mm</t>
-  </si>
-  <si>
-    <t>-15.875mm</t>
-  </si>
-  <si>
-    <t>11.049mm</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>11.811mm</t>
-  </si>
-  <si>
-    <t>-24.384mm</t>
-  </si>
-  <si>
-    <t>13.29mm</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>13.081mm</t>
-  </si>
-  <si>
-    <t>-29.845mm</t>
-  </si>
-  <si>
-    <t>14.56mm</t>
-  </si>
-  <si>
-    <t>p8</t>
-  </si>
-  <si>
-    <t>2.54-1*1P针</t>
-  </si>
-  <si>
-    <t>HDR-TH_1P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>5.842mm</t>
-  </si>
-  <si>
-    <t>-66.392mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>0402F104M500NT</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>13.589mm</t>
-  </si>
-  <si>
-    <t>-32.385mm</t>
-  </si>
-  <si>
-    <t>13.169mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>21.844mm</t>
-  </si>
-  <si>
-    <t>-35.306mm</t>
-  </si>
-  <si>
-    <t>21.424mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>19.072mm</t>
-  </si>
-  <si>
-    <t>-43.982mm</t>
-  </si>
-  <si>
-    <t>19.492mm</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>9.525mm</t>
-  </si>
-  <si>
-    <t>-39.624mm</t>
-  </si>
-  <si>
-    <t>9.228mm</t>
-  </si>
-  <si>
-    <t>-39.327mm</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>8.255mm</t>
-  </si>
-  <si>
-    <t>-64.643mm</t>
-  </si>
-  <si>
-    <t>-65.063mm</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>CL10A106MQ8NNNC</t>
-  </si>
-  <si>
-    <t>21.082mm</t>
-  </si>
-  <si>
-    <t>-44.958mm</t>
-  </si>
-  <si>
-    <t>-44.258mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>RVT1E101M0607</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.2-R-RD</t>
-  </si>
-  <si>
-    <t>5.334mm</t>
-  </si>
-  <si>
-    <t>-74.041mm</t>
-  </si>
-  <si>
-    <t>2.779mm</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>DS1021-1x2SF11-B</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>11.142mm</t>
-  </si>
-  <si>
-    <t>-64.955mm</t>
-  </si>
-  <si>
-    <t>-63.685mm</t>
-  </si>
-  <si>
-    <t>U15</t>
-  </si>
-  <si>
-    <t>23.749mm</t>
-  </si>
-  <si>
-    <t>-58.547mm</t>
-  </si>
-  <si>
-    <t>22.479mm</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>12.294mm</t>
-  </si>
-  <si>
-    <t>-13.281mm</t>
-  </si>
-  <si>
-    <t>11.024mm</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>4.1mm</t>
-  </si>
-  <si>
-    <t>-28.479mm</t>
-  </si>
-  <si>
-    <t>3.68mm</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>0805W8J0103T5E</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>3.937mm</t>
-  </si>
-  <si>
-    <t>-16.764mm</t>
-  </si>
-  <si>
-    <t>-15.764mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>4*4*1.7 贴片</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-L5.2-W5.2-P3.70-LS6.5</t>
-  </si>
-  <si>
-    <t>4.191mm</t>
-  </si>
-  <si>
-    <t>-23.368mm</t>
-  </si>
-  <si>
-    <t>6.041mm</t>
-  </si>
-  <si>
-    <t>-20.268mm</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>S6125-M2-0.5A</t>
-  </si>
-  <si>
-    <t>FUSE-SMD_L6.1-W2.5</t>
-  </si>
-  <si>
-    <t>79.248mm</t>
-  </si>
-  <si>
-    <t>-84.963mm</t>
-  </si>
-  <si>
-    <t>77.48mm</t>
-  </si>
-  <si>
-    <t>-83.195mm</t>
-  </si>
-  <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>10D471K_C8760</t>
-  </si>
-  <si>
-    <t>RES-TH_L12.5-W6.7-P7.50-D1.2</t>
-  </si>
-  <si>
-    <t>78.994mm</t>
-  </si>
-  <si>
-    <t>-93.472mm</t>
-  </si>
-  <si>
-    <t>82.743mm</t>
-  </si>
-  <si>
-    <t>190pF@1kHz</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>CBG321609U600T</t>
-  </si>
-  <si>
-    <t>L1206</t>
-  </si>
-  <si>
-    <t>22.86mm</t>
-  </si>
-  <si>
-    <t>-53.721mm</t>
-  </si>
-  <si>
-    <t>23.986mm</t>
-  </si>
-  <si>
-    <t>-52.595mm</t>
-  </si>
-  <si>
-    <t>zdc</t>
-  </si>
-  <si>
-    <t>29.591mm</t>
-  </si>
-  <si>
-    <t>-53.975mm</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>WJ124-3.81-04P-14-00A</t>
-  </si>
-  <si>
-    <t>CONN-TH_4P-P3.81_KF124-3.81-4P</t>
-  </si>
-  <si>
-    <t>93.599mm</t>
-  </si>
-  <si>
-    <t>-20.955mm</t>
-  </si>
-  <si>
-    <t>-15.24mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>KT-0603Y</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD</t>
-  </si>
-  <si>
-    <t>29.905mm</t>
-  </si>
-  <si>
-    <t>-31.518mm</t>
-  </si>
-  <si>
-    <t>29.154mm</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>-28.347mm</t>
-  </si>
-  <si>
-    <t>LED3</t>
-  </si>
-  <si>
-    <t>-25.176mm</t>
-  </si>
-  <si>
-    <t>LED4</t>
-  </si>
-  <si>
-    <t>-22.005mm</t>
-  </si>
-  <si>
-    <t>LED5</t>
-  </si>
-  <si>
-    <t>-18.834mm</t>
-  </si>
-  <si>
-    <t>R35</t>
-  </si>
-  <si>
-    <t>0402WGF1401TCE</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>27.322mm</t>
-  </si>
-  <si>
-    <t>-18.961mm</t>
-  </si>
-  <si>
-    <t>27.755mm</t>
-  </si>
-  <si>
-    <t>1.4kΩ</t>
-  </si>
-  <si>
-    <t>R34</t>
-  </si>
-  <si>
-    <t>-22.134mm</t>
-  </si>
-  <si>
-    <t>R33</t>
-  </si>
-  <si>
-    <t>27.449mm</t>
-  </si>
-  <si>
-    <t>-25.308mm</t>
-  </si>
-  <si>
-    <t>27.882mm</t>
-  </si>
-  <si>
-    <t>R32</t>
-  </si>
-  <si>
-    <t>27.195mm</t>
-  </si>
-  <si>
-    <t>-28.355mm</t>
-  </si>
-  <si>
-    <t>27.628mm</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
-    <t>-31.528mm</t>
-  </si>
-  <si>
-    <t>R36</t>
-  </si>
-  <si>
-    <t>0805W8F2200T5E</t>
-  </si>
-  <si>
-    <t>37.664mm</t>
-  </si>
-  <si>
-    <t>-10.235mm</t>
-  </si>
-  <si>
-    <t>36.664mm</t>
-  </si>
-  <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R37</t>
-  </si>
-  <si>
-    <t>36.013mm</t>
-  </si>
-  <si>
-    <t>-25.168mm</t>
-  </si>
-  <si>
-    <t>35.013mm</t>
-  </si>
-  <si>
-    <t>R38</t>
-  </si>
-  <si>
-    <t>-39.084mm</t>
-  </si>
-  <si>
-    <t>R39</t>
-  </si>
-  <si>
-    <t>36.267mm</t>
-  </si>
-  <si>
-    <t>-53.509mm</t>
-  </si>
-  <si>
-    <t>35.267mm</t>
-  </si>
-  <si>
-    <t>R40</t>
-  </si>
-  <si>
-    <t>38.172mm</t>
-  </si>
-  <si>
-    <t>-67.172mm</t>
-  </si>
-  <si>
-    <t>-66.172mm</t>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>52.451mm</t>
+  </si>
+  <si>
+    <t>50.001mm</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>-49.784mm</t>
+  </si>
+  <si>
+    <t>R47</t>
+  </si>
+  <si>
+    <t>51.816mm</t>
+  </si>
+  <si>
+    <t>-63.5mm</t>
+  </si>
+  <si>
+    <t>49.366mm</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>52.324mm</t>
+  </si>
+  <si>
+    <t>-78.105mm</t>
+  </si>
+  <si>
+    <t>49.874mm</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>MOC3053SM</t>
+  </si>
+  <si>
+    <t>MOC3053_NoPin5</t>
+  </si>
+  <si>
+    <t>44.577mm</t>
+  </si>
+  <si>
+    <t>-29.718mm</t>
+  </si>
+  <si>
+    <t>39.977mm</t>
+  </si>
+  <si>
+    <t>-27.178mm</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>44.323mm</t>
+  </si>
+  <si>
+    <t>-57.912mm</t>
+  </si>
+  <si>
+    <t>39.723mm</t>
+  </si>
+  <si>
+    <t>-55.372mm</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>-43.942mm</t>
+  </si>
+  <si>
+    <t>-41.402mm</t>
   </si>
   <si>
     <t>U17</t>
   </si>
   <si>
-    <t>MOC3053SM</t>
-  </si>
-  <si>
-    <t>SMD-6_L8.8-W6.4-P2.54-LS9.4-BL</t>
-  </si>
-  <si>
-    <t>44.577mm</t>
-  </si>
-  <si>
-    <t>-16.002mm</t>
-  </si>
-  <si>
-    <t>39.977mm</t>
-  </si>
-  <si>
-    <t>-13.462mm</t>
-  </si>
-  <si>
-    <t>U18</t>
-  </si>
-  <si>
-    <t>-29.718mm</t>
-  </si>
-  <si>
-    <t>-27.178mm</t>
-  </si>
-  <si>
-    <t>U19</t>
-  </si>
-  <si>
-    <t>44.45mm</t>
-  </si>
-  <si>
-    <t>-44.45mm</t>
-  </si>
-  <si>
-    <t>39.85mm</t>
-  </si>
-  <si>
-    <t>-41.91mm</t>
-  </si>
-  <si>
-    <t>U20</t>
-  </si>
-  <si>
-    <t>44.323mm</t>
-  </si>
-  <si>
-    <t>-57.912mm</t>
-  </si>
-  <si>
-    <t>39.723mm</t>
-  </si>
-  <si>
-    <t>-55.372mm</t>
+    <t>44.704mm</t>
+  </si>
+  <si>
+    <t>-14.478mm</t>
+  </si>
+  <si>
+    <t>40.104mm</t>
+  </si>
+  <si>
+    <t>-11.938mm</t>
   </si>
   <si>
     <t>U21</t>
   </si>
   <si>
-    <t>44.704mm</t>
-  </si>
-  <si>
-    <t>-74.168mm</t>
-  </si>
-  <si>
-    <t>40.104mm</t>
-  </si>
-  <si>
-    <t>-71.628mm</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>1210W2F4702T5E</t>
-  </si>
-  <si>
-    <t>R1210</t>
-  </si>
-  <si>
-    <t>66.167mm</t>
-  </si>
-  <si>
-    <t>-84.455mm</t>
-  </si>
-  <si>
-    <t>65.148mm</t>
-  </si>
-  <si>
-    <t>-83.436mm</t>
-  </si>
-  <si>
-    <t>47kΩ</t>
-  </si>
-  <si>
-    <t>R42</t>
-  </si>
-  <si>
-    <t>KNP03SJ0100A10</t>
-  </si>
-  <si>
-    <t>RES-TH_BD5.0-L15.5-P19.50-D0.7</t>
-  </si>
-  <si>
-    <t>60.071mm</t>
-  </si>
-  <si>
-    <t>-95.504mm</t>
-  </si>
-  <si>
-    <t>50.653mm</t>
-  </si>
-  <si>
-    <t>-98.027mm</t>
-  </si>
-  <si>
-    <t>10Ω</t>
-  </si>
-  <si>
-    <t>R43</t>
-  </si>
-  <si>
-    <t>61.468mm</t>
-  </si>
-  <si>
-    <t>-89.154mm</t>
-  </si>
-  <si>
-    <t>62.909mm</t>
+    <t>-70.231mm</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>7.578mm</t>
+  </si>
+  <si>
+    <t>-89.431mm</t>
+  </si>
+  <si>
+    <t>7.158mm</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>7.62mm</t>
+  </si>
+  <si>
+    <t>-88.011mm</t>
+  </si>
+  <si>
+    <t>8.32mm</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>3.327mm</t>
+  </si>
+  <si>
+    <t>-81.49mm</t>
+  </si>
+  <si>
+    <t>-81.91mm</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3V_C2688239</t>
+  </si>
+  <si>
+    <t>SOT-223-4_L6.5-W3.5-P2.30-LS7.0-BR</t>
+  </si>
+  <si>
+    <t>-83.185mm</t>
+  </si>
+  <si>
+    <t>5.293mm</t>
+  </si>
+  <si>
+    <t>-80.885mm</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3V</t>
+  </si>
+  <si>
+    <t>U23</t>
+  </si>
+  <si>
+    <t>6.223mm</t>
+  </si>
+  <si>
+    <t>7.493mm</t>
+  </si>
+  <si>
+    <t>p9</t>
+  </si>
+  <si>
+    <t>10.795mm</t>
+  </si>
+  <si>
+    <t>-89.861mm</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -1836,10 +1902,10 @@
         <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="s">
         <v>20</v>
@@ -1851,7 +1917,7 @@
         <v>35</v>
       </c>
       <c r="N9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1859,72 +1925,72 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>180</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" t="s">
         <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1933,42 +1999,42 @@
         <v>20</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M11" t="s">
         <v>35</v>
       </c>
       <c r="N11" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1977,42 +2043,42 @@
         <v>20</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M12" t="s">
         <v>35</v>
       </c>
       <c r="N12" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2021,133 +2087,133 @@
         <v>20</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="M13" t="s">
         <v>35</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" t="s">
         <v>20</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15">
         <v>90</v>
       </c>
-      <c r="J15">
-        <v>4</v>
-      </c>
-      <c r="K15" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15">
-        <v>180</v>
-      </c>
       <c r="M15" t="s">
         <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="K16" t="s">
         <v>20</v>
@@ -2159,36 +2225,36 @@
         <v>35</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -2197,62 +2263,62 @@
         <v>20</v>
       </c>
       <c r="L17">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="M17" t="s">
         <v>35</v>
       </c>
       <c r="N17" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I18" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18" t="s">
         <v>20</v>
       </c>
       <c r="L18">
-        <v>315</v>
+        <v>90</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
@@ -2261,22 +2327,22 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2285,7 +2351,7 @@
         <v>20</v>
       </c>
       <c r="L19">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M19" t="s">
         <v>21</v>
@@ -2296,31 +2362,31 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -2329,98 +2395,98 @@
         <v>20</v>
       </c>
       <c r="L20">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s">
         <v>35</v>
       </c>
       <c r="N20" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G21" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J21">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
       </c>
       <c r="L21">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
         <v>35</v>
       </c>
       <c r="N21" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="s">
         <v>20</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N22" t="s">
         <v>133</v>
@@ -2428,78 +2494,78 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K24" t="s">
         <v>20</v>
@@ -2508,39 +2574,39 @@
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N24" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2555,36 +2621,36 @@
         <v>35</v>
       </c>
       <c r="N25" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G26" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H26" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I26" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2593,86 +2659,86 @@
         <v>20</v>
       </c>
       <c r="L26">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="M26" t="s">
         <v>35</v>
       </c>
       <c r="N26" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M27" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H28" t="s">
         <v>163</v>
       </c>
       <c r="I28" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -2681,42 +2747,42 @@
         <v>20</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s">
         <v>35</v>
       </c>
       <c r="N28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -2725,42 +2791,42 @@
         <v>20</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s">
         <v>35</v>
       </c>
       <c r="N29" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G30" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2769,86 +2835,86 @@
         <v>20</v>
       </c>
       <c r="L30">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" t="s">
+        <v>183</v>
+      </c>
+      <c r="I31" t="s">
+        <v>182</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" t="s">
         <v>175</v>
-      </c>
-      <c r="F31" t="s">
-        <v>174</v>
-      </c>
-      <c r="G31" t="s">
-        <v>175</v>
-      </c>
-      <c r="H31" t="s">
-        <v>176</v>
-      </c>
-      <c r="I31" t="s">
-        <v>177</v>
-      </c>
-      <c r="J31">
-        <v>2</v>
-      </c>
-      <c r="K31" t="s">
-        <v>20</v>
-      </c>
-      <c r="L31">
-        <v>315</v>
-      </c>
-      <c r="M31" t="s">
-        <v>35</v>
-      </c>
-      <c r="N31" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I32" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -2857,42 +2923,42 @@
         <v>20</v>
       </c>
       <c r="L32">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F33" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2901,42 +2967,42 @@
         <v>20</v>
       </c>
       <c r="L33">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M33" t="s">
         <v>35</v>
       </c>
       <c r="N33" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F34" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2945,45 +3011,45 @@
         <v>20</v>
       </c>
       <c r="L34">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s">
         <v>35</v>
       </c>
       <c r="N34" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G35" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I35" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="s">
         <v>20</v>
@@ -2992,39 +3058,39 @@
         <v>270</v>
       </c>
       <c r="M35" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N35" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E36" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F36" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G36" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H36" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="I36" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -3033,42 +3099,42 @@
         <v>20</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N36" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F37" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G37" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="H37" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I37" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -3077,42 +3143,42 @@
         <v>20</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s">
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F38" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="H38" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="I38" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="J38">
         <v>2</v>
@@ -3121,86 +3187,86 @@
         <v>20</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M38" t="s">
         <v>35</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F39" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="G39" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="H39" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="I39" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" t="s">
         <v>20</v>
       </c>
       <c r="L39">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="M39" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="F40" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G40" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H40" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I40" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="J40">
         <v>4</v>
@@ -3209,42 +3275,42 @@
         <v>20</v>
       </c>
       <c r="L40">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D41" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F41" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G41" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H41" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I41" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -3253,42 +3319,42 @@
         <v>20</v>
       </c>
       <c r="L41">
-        <v>315</v>
+        <v>180</v>
       </c>
       <c r="M41" t="s">
         <v>35</v>
       </c>
       <c r="N41" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F42" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G42" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H42" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I42" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -3300,40 +3366,40 @@
         <v>180</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" t="s">
+        <v>246</v>
+      </c>
+      <c r="F43" t="s">
+        <v>240</v>
+      </c>
+      <c r="G43" t="s">
+        <v>246</v>
+      </c>
+      <c r="H43" t="s">
         <v>242</v>
       </c>
-      <c r="C43" t="s">
-        <v>243</v>
-      </c>
-      <c r="D43" t="s">
-        <v>244</v>
-      </c>
-      <c r="E43" t="s">
-        <v>245</v>
-      </c>
-      <c r="F43" t="s">
-        <v>244</v>
-      </c>
-      <c r="G43" t="s">
-        <v>245</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>246</v>
       </c>
-      <c r="I43" t="s">
-        <v>247</v>
-      </c>
       <c r="J43">
         <v>2</v>
       </c>
@@ -3341,130 +3407,130 @@
         <v>20</v>
       </c>
       <c r="L43">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M43" t="s">
         <v>35</v>
       </c>
       <c r="N43" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" t="s">
         <v>248</v>
       </c>
-      <c r="B44" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" t="s">
-        <v>249</v>
-      </c>
-      <c r="E44" t="s">
-        <v>250</v>
-      </c>
       <c r="F44" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="G44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H44" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" t="s">
         <v>20</v>
       </c>
       <c r="L44">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N44" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C45" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F45" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="G45" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H45" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="I45" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" t="s">
         <v>20</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M45" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N45" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E46" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G46" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H46" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I46" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -3479,36 +3545,36 @@
         <v>35</v>
       </c>
       <c r="N46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C47" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" t="s">
         <v>259</v>
       </c>
-      <c r="D47" t="s">
-        <v>260</v>
-      </c>
-      <c r="E47" t="s">
-        <v>264</v>
-      </c>
       <c r="F47" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G47" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H47" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I47" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3523,36 +3589,36 @@
         <v>35</v>
       </c>
       <c r="N47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E48" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G48" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H48" t="s">
+        <v>263</v>
+      </c>
+      <c r="I48" t="s">
         <v>262</v>
-      </c>
-      <c r="I48" t="s">
-        <v>266</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3567,36 +3633,36 @@
         <v>35</v>
       </c>
       <c r="N48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>264</v>
+      </c>
+      <c r="B49" t="s">
+        <v>252</v>
+      </c>
+      <c r="C49" t="s">
+        <v>253</v>
+      </c>
+      <c r="D49" t="s">
+        <v>265</v>
+      </c>
+      <c r="E49" t="s">
+        <v>266</v>
+      </c>
+      <c r="F49" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" t="s">
+        <v>266</v>
+      </c>
+      <c r="H49" t="s">
         <v>267</v>
       </c>
-      <c r="B49" t="s">
-        <v>258</v>
-      </c>
-      <c r="C49" t="s">
-        <v>259</v>
-      </c>
-      <c r="D49" t="s">
-        <v>260</v>
-      </c>
-      <c r="E49" t="s">
-        <v>268</v>
-      </c>
-      <c r="F49" t="s">
-        <v>260</v>
-      </c>
-      <c r="G49" t="s">
-        <v>268</v>
-      </c>
-      <c r="H49" t="s">
-        <v>262</v>
-      </c>
       <c r="I49" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -3611,36 +3677,36 @@
         <v>35</v>
       </c>
       <c r="N49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" t="s">
+        <v>253</v>
+      </c>
+      <c r="D50" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" t="s">
         <v>269</v>
       </c>
-      <c r="B50" t="s">
-        <v>258</v>
-      </c>
-      <c r="C50" t="s">
-        <v>259</v>
-      </c>
-      <c r="D50" t="s">
-        <v>260</v>
-      </c>
-      <c r="E50" t="s">
-        <v>270</v>
-      </c>
       <c r="F50" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H50" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -3655,80 +3721,80 @@
         <v>35</v>
       </c>
       <c r="N50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>270</v>
+      </c>
+      <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" t="s">
         <v>272</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>273</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
+        <v>272</v>
+      </c>
+      <c r="G51" t="s">
+        <v>273</v>
+      </c>
+      <c r="H51" t="s">
         <v>274</v>
       </c>
-      <c r="E51" t="s">
+      <c r="I51" t="s">
+        <v>273</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
+      </c>
+      <c r="N51" t="s">
         <v>275</v>
-      </c>
-      <c r="F51" t="s">
-        <v>274</v>
-      </c>
-      <c r="G51" t="s">
-        <v>275</v>
-      </c>
-      <c r="H51" t="s">
-        <v>276</v>
-      </c>
-      <c r="I51" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51">
-        <v>2</v>
-      </c>
-      <c r="K51" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51">
-        <v>180</v>
-      </c>
-      <c r="M51" t="s">
-        <v>35</v>
-      </c>
-      <c r="N51" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>276</v>
+      </c>
+      <c r="B52" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52" t="s">
+        <v>194</v>
+      </c>
+      <c r="D52" t="s">
+        <v>277</v>
+      </c>
+      <c r="E52" t="s">
         <v>278</v>
       </c>
-      <c r="B52" t="s">
-        <v>272</v>
-      </c>
-      <c r="C52" t="s">
-        <v>273</v>
-      </c>
-      <c r="D52" t="s">
-        <v>274</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>277</v>
+      </c>
+      <c r="G52" t="s">
+        <v>278</v>
+      </c>
+      <c r="H52" t="s">
         <v>279</v>
       </c>
-      <c r="F52" t="s">
-        <v>274</v>
-      </c>
-      <c r="G52" t="s">
-        <v>279</v>
-      </c>
-      <c r="H52" t="s">
-        <v>276</v>
-      </c>
       <c r="I52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3737,13 +3803,13 @@
         <v>20</v>
       </c>
       <c r="L52">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M52" t="s">
         <v>35</v>
       </c>
       <c r="N52" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -3751,28 +3817,28 @@
         <v>280</v>
       </c>
       <c r="B53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C53" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
+        <v>277</v>
+      </c>
+      <c r="E53" t="s">
         <v>281</v>
       </c>
-      <c r="E53" t="s">
-        <v>282</v>
-      </c>
       <c r="F53" t="s">
+        <v>277</v>
+      </c>
+      <c r="G53" t="s">
         <v>281</v>
       </c>
-      <c r="G53" t="s">
-        <v>282</v>
-      </c>
       <c r="H53" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I53" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3781,42 +3847,42 @@
         <v>20</v>
       </c>
       <c r="L53">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M53" t="s">
         <v>35</v>
       </c>
       <c r="N53" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>282</v>
+      </c>
+      <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" t="s">
+        <v>194</v>
+      </c>
+      <c r="D54" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" t="s">
         <v>284</v>
       </c>
-      <c r="B54" t="s">
-        <v>272</v>
-      </c>
-      <c r="C54" t="s">
-        <v>273</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>283</v>
+      </c>
+      <c r="G54" t="s">
+        <v>284</v>
+      </c>
+      <c r="H54" t="s">
         <v>285</v>
       </c>
-      <c r="E54" t="s">
-        <v>286</v>
-      </c>
-      <c r="F54" t="s">
-        <v>285</v>
-      </c>
-      <c r="G54" t="s">
-        <v>286</v>
-      </c>
-      <c r="H54" t="s">
-        <v>287</v>
-      </c>
       <c r="I54" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3825,39 +3891,39 @@
         <v>20</v>
       </c>
       <c r="L54">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M54" t="s">
         <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>286</v>
+      </c>
+      <c r="B55" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" t="s">
+        <v>287</v>
+      </c>
+      <c r="E55" t="s">
         <v>288</v>
       </c>
-      <c r="B55" t="s">
-        <v>272</v>
-      </c>
-      <c r="C55" t="s">
-        <v>273</v>
-      </c>
-      <c r="D55" t="s">
-        <v>274</v>
-      </c>
-      <c r="E55" t="s">
-        <v>289</v>
-      </c>
       <c r="F55" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="G55" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H55" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="I55" t="s">
         <v>289</v>
@@ -3869,13 +3935,13 @@
         <v>20</v>
       </c>
       <c r="L55">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M55" t="s">
         <v>35</v>
       </c>
       <c r="N55" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -3886,25 +3952,25 @@
         <v>291</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="D56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F56" t="s">
         <v>293</v>
       </c>
-      <c r="F56" t="s">
-        <v>292</v>
-      </c>
       <c r="G56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I56" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3913,42 +3979,42 @@
         <v>20</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="M56" t="s">
         <v>35</v>
       </c>
       <c r="N56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B57" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E57" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F57" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G57" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H57" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I57" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3957,86 +4023,86 @@
         <v>20</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s">
         <v>291</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="D58" t="s">
+        <v>307</v>
+      </c>
+      <c r="E58" t="s">
+        <v>308</v>
+      </c>
+      <c r="F58" t="s">
+        <v>307</v>
+      </c>
+      <c r="G58" t="s">
+        <v>308</v>
+      </c>
+      <c r="H58" t="s">
+        <v>309</v>
+      </c>
+      <c r="I58" t="s">
+        <v>308</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58">
+        <v>180</v>
+      </c>
+      <c r="M58" t="s">
+        <v>35</v>
+      </c>
+      <c r="N58" t="s">
         <v>297</v>
-      </c>
-      <c r="E58" t="s">
-        <v>301</v>
-      </c>
-      <c r="F58" t="s">
-        <v>297</v>
-      </c>
-      <c r="G58" t="s">
-        <v>301</v>
-      </c>
-      <c r="H58" t="s">
-        <v>299</v>
-      </c>
-      <c r="I58" t="s">
-        <v>301</v>
-      </c>
-      <c r="J58">
-        <v>2</v>
-      </c>
-      <c r="K58" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58" t="s">
-        <v>35</v>
-      </c>
-      <c r="N58" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E59" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="F59" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G59" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="H59" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="I59" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -4051,36 +4117,36 @@
         <v>35</v>
       </c>
       <c r="N59" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="E60" t="s">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="F60" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G60" t="s">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="H60" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="I60" t="s">
-        <v>309</v>
+        <v>146</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -4089,18 +4155,18 @@
         <v>20</v>
       </c>
       <c r="L60">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M60" t="s">
         <v>35</v>
       </c>
       <c r="N60" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s">
         <v>311</v>
@@ -4112,39 +4178,39 @@
         <v>313</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F61" t="s">
         <v>313</v>
       </c>
       <c r="G61" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H61" t="s">
         <v>315</v>
       </c>
       <c r="I61" t="s">
+        <v>321</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
+        <v>35</v>
+      </c>
+      <c r="N61" t="s">
         <v>316</v>
-      </c>
-      <c r="J61">
-        <v>6</v>
-      </c>
-      <c r="K61" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61">
-        <v>270</v>
-      </c>
-      <c r="M61" t="s">
-        <v>35</v>
-      </c>
-      <c r="N61" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B62" t="s">
         <v>311</v>
@@ -4153,42 +4219,42 @@
         <v>312</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="E62" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F62" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="G62" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="H62" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="I62" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K62" t="s">
         <v>20</v>
       </c>
       <c r="L62">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M62" t="s">
         <v>35</v>
       </c>
       <c r="N62" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B63" t="s">
         <v>311</v>
@@ -4197,69 +4263,69 @@
         <v>312</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E63" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F63" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G63" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H63" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I63" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K63" t="s">
         <v>20</v>
       </c>
       <c r="L63">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M63" t="s">
         <v>35</v>
       </c>
       <c r="N63" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B64" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C64" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E64" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F64" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="G64" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="H64" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="I64" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" t="s">
         <v>20</v>
@@ -4271,39 +4337,39 @@
         <v>35</v>
       </c>
       <c r="N64" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C65" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E65" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F65" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="G65" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="H65" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="I65" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" t="s">
         <v>20</v>
@@ -4315,62 +4381,62 @@
         <v>35</v>
       </c>
       <c r="N65" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B66" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C66" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D66" t="s">
         <v>338</v>
       </c>
       <c r="E66" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F66" t="s">
         <v>338</v>
       </c>
       <c r="G66" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H66" t="s">
         <v>340</v>
       </c>
       <c r="I66" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
       </c>
       <c r="L66">
-        <v>315</v>
+        <v>270</v>
       </c>
       <c r="M66" t="s">
         <v>35</v>
       </c>
       <c r="N66" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B67" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C67" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
         <v>346</v>
@@ -4391,63 +4457,327 @@
         <v>349</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K67" t="s">
         <v>20</v>
       </c>
       <c r="L67">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="M67" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N67" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" t="s">
+        <v>331</v>
+      </c>
+      <c r="C68" t="s">
+        <v>332</v>
+      </c>
+      <c r="D68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E68" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68" t="s">
+        <v>333</v>
+      </c>
+      <c r="G68" t="s">
+        <v>171</v>
+      </c>
+      <c r="H68" t="s">
+        <v>335</v>
+      </c>
+      <c r="I68" t="s">
         <v>351</v>
       </c>
-      <c r="B68" t="s">
-        <v>336</v>
-      </c>
-      <c r="C68" t="s">
-        <v>337</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L68">
+        <v>270</v>
+      </c>
+      <c r="M68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N68" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>352</v>
       </c>
-      <c r="E68" t="s">
+      <c r="B69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>139</v>
+      </c>
+      <c r="D69" t="s">
         <v>353</v>
       </c>
-      <c r="F68" t="s">
-        <v>352</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="E69" t="s">
+        <v>354</v>
+      </c>
+      <c r="F69" t="s">
         <v>353</v>
       </c>
-      <c r="H68" t="s">
+      <c r="G69" t="s">
         <v>354</v>
       </c>
-      <c r="I68" t="s">
-        <v>353</v>
-      </c>
-      <c r="J68">
-        <v>2</v>
-      </c>
-      <c r="K68" t="s">
-        <v>20</v>
-      </c>
-      <c r="L68">
+      <c r="H69" t="s">
+        <v>355</v>
+      </c>
+      <c r="I69" t="s">
+        <v>354</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>356</v>
+      </c>
+      <c r="B70" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>357</v>
+      </c>
+      <c r="E70" t="s">
+        <v>358</v>
+      </c>
+      <c r="F70" t="s">
+        <v>357</v>
+      </c>
+      <c r="G70" t="s">
+        <v>358</v>
+      </c>
+      <c r="H70" t="s">
+        <v>359</v>
+      </c>
+      <c r="I70" t="s">
+        <v>358</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70">
         <v>180</v>
       </c>
-      <c r="M68" t="s">
-        <v>35</v>
-      </c>
-      <c r="N68" t="s">
-        <v>342</v>
+      <c r="M70" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>360</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" t="s">
+        <v>361</v>
+      </c>
+      <c r="E71" t="s">
+        <v>362</v>
+      </c>
+      <c r="F71" t="s">
+        <v>361</v>
+      </c>
+      <c r="G71" t="s">
+        <v>362</v>
+      </c>
+      <c r="H71" t="s">
+        <v>361</v>
+      </c>
+      <c r="I71" t="s">
+        <v>363</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>20</v>
+      </c>
+      <c r="L71">
+        <v>90</v>
+      </c>
+      <c r="M71" t="s">
+        <v>35</v>
+      </c>
+      <c r="N71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>364</v>
+      </c>
+      <c r="B72" t="s">
+        <v>365</v>
+      </c>
+      <c r="C72" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" t="s">
+        <v>367</v>
+      </c>
+      <c r="F72" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s">
+        <v>367</v>
+      </c>
+      <c r="H72" t="s">
+        <v>368</v>
+      </c>
+      <c r="I72" t="s">
+        <v>369</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72" t="s">
+        <v>20</v>
+      </c>
+      <c r="L72">
+        <v>180</v>
+      </c>
+      <c r="M72" t="s">
+        <v>35</v>
+      </c>
+      <c r="N72" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>371</v>
+      </c>
+      <c r="B73" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D73" t="s">
+        <v>372</v>
+      </c>
+      <c r="E73" t="s">
+        <v>328</v>
+      </c>
+      <c r="F73" t="s">
+        <v>372</v>
+      </c>
+      <c r="G73" t="s">
+        <v>328</v>
+      </c>
+      <c r="H73" t="s">
+        <v>373</v>
+      </c>
+      <c r="I73" t="s">
+        <v>328</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73" t="s">
+        <v>20</v>
+      </c>
+      <c r="L73">
+        <v>180</v>
+      </c>
+      <c r="M73" t="s">
+        <v>21</v>
+      </c>
+      <c r="N73" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>374</v>
+      </c>
+      <c r="B74" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" t="s">
+        <v>134</v>
+      </c>
+      <c r="D74" t="s">
+        <v>375</v>
+      </c>
+      <c r="E74" t="s">
+        <v>376</v>
+      </c>
+      <c r="F74" t="s">
+        <v>375</v>
+      </c>
+      <c r="G74" t="s">
+        <v>376</v>
+      </c>
+      <c r="H74" t="s">
+        <v>375</v>
+      </c>
+      <c r="I74" t="s">
+        <v>376</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>20</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/PickAndPlace.xlsx
+++ b/PCB/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB2_2026-04-13" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB2_2026-04-22" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="425">
   <si>
     <t>Designator</t>
   </si>
@@ -379,7 +379,7 @@
     <t>17.399mm</t>
   </si>
   <si>
-    <t>-15.875mm</t>
+    <t>-16.891mm</t>
   </si>
   <si>
     <t>11.049mm</t>
@@ -451,525 +451,525 @@
     <t>21.844mm</t>
   </si>
   <si>
+    <t>-34.798mm</t>
+  </si>
+  <si>
+    <t>21.424mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>20.828mm</t>
+  </si>
+  <si>
+    <t>-44.958mm</t>
+  </si>
+  <si>
+    <t>-44.538mm</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>9.525mm</t>
+  </si>
+  <si>
+    <t>-39.624mm</t>
+  </si>
+  <si>
+    <t>9.228mm</t>
+  </si>
+  <si>
+    <t>-39.327mm</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>8.255mm</t>
+  </si>
+  <si>
+    <t>-64.643mm</t>
+  </si>
+  <si>
+    <t>-65.063mm</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>CL10A106MQ8NNNC</t>
+  </si>
+  <si>
+    <t>22.352mm</t>
+  </si>
+  <si>
+    <t>-44.258mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>RVT1E101M0607</t>
+  </si>
+  <si>
+    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.2-R-RD</t>
+  </si>
+  <si>
+    <t>5.207mm</t>
+  </si>
+  <si>
+    <t>-72.771mm</t>
+  </si>
+  <si>
+    <t>2.652mm</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>DS1021-1x2SF11-B</t>
+  </si>
+  <si>
+    <t>HDR-TH_2P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>11.142mm</t>
+  </si>
+  <si>
+    <t>-64.955mm</t>
+  </si>
+  <si>
+    <t>-63.685mm</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>23.749mm</t>
+  </si>
+  <si>
+    <t>-58.547mm</t>
+  </si>
+  <si>
+    <t>22.479mm</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>12.294mm</t>
+  </si>
+  <si>
+    <t>-14.297mm</t>
+  </si>
+  <si>
+    <t>11.024mm</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>4.1mm</t>
+  </si>
+  <si>
+    <t>-28.479mm</t>
+  </si>
+  <si>
+    <t>3.68mm</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>0805W8J0103T5E</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>3.937mm</t>
+  </si>
+  <si>
+    <t>-16.764mm</t>
+  </si>
+  <si>
+    <t>-15.764mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>4*4*1.7 贴片</t>
+  </si>
+  <si>
+    <t>SW-SMD_4P-L5.2-W5.2-P3.70-LS6.5</t>
+  </si>
+  <si>
+    <t>4.191mm</t>
+  </si>
+  <si>
+    <t>-23.368mm</t>
+  </si>
+  <si>
+    <t>6.041mm</t>
+  </si>
+  <si>
+    <t>-20.268mm</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>S6125-M2-0.5A</t>
+  </si>
+  <si>
+    <t>FUSE-SMD_L6.1-W2.5</t>
+  </si>
+  <si>
+    <t>88.9mm</t>
+  </si>
+  <si>
+    <t>-73.152mm</t>
+  </si>
+  <si>
+    <t>87.132mm</t>
+  </si>
+  <si>
+    <t>-71.384mm</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>10D471K_C8760</t>
+  </si>
+  <si>
+    <t>RES-TH_L12.5-W6.7-P7.50-D1.2</t>
+  </si>
+  <si>
+    <t>86.995mm</t>
+  </si>
+  <si>
+    <t>-82.423mm</t>
+  </si>
+  <si>
+    <t>83.374mm</t>
+  </si>
+  <si>
+    <t>-81.453mm</t>
+  </si>
+  <si>
+    <t>190pF@1kHz</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>CBG321609U600T</t>
+  </si>
+  <si>
+    <t>L1206</t>
+  </si>
+  <si>
+    <t>22.86mm</t>
+  </si>
+  <si>
+    <t>-53.721mm</t>
+  </si>
+  <si>
+    <t>23.986mm</t>
+  </si>
+  <si>
+    <t>-52.595mm</t>
+  </si>
+  <si>
+    <t>zdc</t>
+  </si>
+  <si>
+    <t>29.591mm</t>
+  </si>
+  <si>
+    <t>-53.975mm</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>WJ124-3.81-04P-14-00A</t>
+  </si>
+  <si>
+    <t>CONN-TH_4P-P3.81_KF124-3.81-4P</t>
+  </si>
+  <si>
+    <t>93.599mm</t>
+  </si>
+  <si>
+    <t>-20.955mm</t>
+  </si>
+  <si>
+    <t>-15.24mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>KT-0603Y</t>
+  </si>
+  <si>
+    <t>LED0603-R-RD</t>
+  </si>
+  <si>
+    <t>29.905mm</t>
+  </si>
+  <si>
+    <t>-31.518mm</t>
+  </si>
+  <si>
+    <t>29.154mm</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>-28.347mm</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>-25.176mm</t>
+  </si>
+  <si>
+    <t>LED4</t>
+  </si>
+  <si>
+    <t>-22.005mm</t>
+  </si>
+  <si>
+    <t>LED5</t>
+  </si>
+  <si>
+    <t>-18.834mm</t>
+  </si>
+  <si>
+    <t>R35</t>
+  </si>
+  <si>
+    <t>0402WGF1401TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>27.322mm</t>
+  </si>
+  <si>
+    <t>-18.961mm</t>
+  </si>
+  <si>
+    <t>27.755mm</t>
+  </si>
+  <si>
+    <t>1.4kΩ</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>-22.134mm</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>27.449mm</t>
+  </si>
+  <si>
+    <t>-25.308mm</t>
+  </si>
+  <si>
+    <t>27.882mm</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>27.195mm</t>
+  </si>
+  <si>
+    <t>-28.355mm</t>
+  </si>
+  <si>
+    <t>27.628mm</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>-31.528mm</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>0805W8F2200T5E</t>
+  </si>
+  <si>
+    <t>34.489mm</t>
+  </si>
+  <si>
+    <t>-14.045mm</t>
+  </si>
+  <si>
+    <t>33.489mm</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>36.013mm</t>
+  </si>
+  <si>
+    <t>-25.168mm</t>
+  </si>
+  <si>
+    <t>35.013mm</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
+    <t>-39.084mm</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>36.267mm</t>
+  </si>
+  <si>
+    <t>-53.509mm</t>
+  </si>
+  <si>
+    <t>35.267mm</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>38.354mm</t>
+  </si>
+  <si>
+    <t>-65.405mm</t>
+  </si>
+  <si>
+    <t>-64.405mm</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>1210W2F4702T5E</t>
+  </si>
+  <si>
+    <t>R1210</t>
+  </si>
+  <si>
+    <t>66.167mm</t>
+  </si>
+  <si>
+    <t>-84.455mm</t>
+  </si>
+  <si>
+    <t>65.148mm</t>
+  </si>
+  <si>
+    <t>-83.436mm</t>
+  </si>
+  <si>
+    <t>47kΩ</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>KNP03SJ0100A10</t>
+  </si>
+  <si>
+    <t>RES-TH_BD5.0-L15.5-P19.50-D0.7</t>
+  </si>
+  <si>
+    <t>79.121mm</t>
+  </si>
+  <si>
+    <t>-91.821mm</t>
+  </si>
+  <si>
+    <t>69.703mm</t>
+  </si>
+  <si>
+    <t>-94.344mm</t>
+  </si>
+  <si>
+    <t>10Ω</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>61.468mm</t>
+  </si>
+  <si>
+    <t>-89.154mm</t>
+  </si>
+  <si>
+    <t>62.909mm</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>MMB02070C4700FB200</t>
+  </si>
+  <si>
+    <t>R0207</t>
+  </si>
+  <si>
+    <t>52.07mm</t>
+  </si>
+  <si>
+    <t>-20.32mm</t>
+  </si>
+  <si>
+    <t>49.62mm</t>
+  </si>
+  <si>
+    <t>470Ω</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>52.451mm</t>
+  </si>
+  <si>
     <t>-35.306mm</t>
   </si>
   <si>
-    <t>21.424mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>19.072mm</t>
-  </si>
-  <si>
-    <t>-43.982mm</t>
-  </si>
-  <si>
-    <t>19.492mm</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>9.525mm</t>
-  </si>
-  <si>
-    <t>-39.624mm</t>
-  </si>
-  <si>
-    <t>9.228mm</t>
-  </si>
-  <si>
-    <t>-39.327mm</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>8.255mm</t>
-  </si>
-  <si>
-    <t>-64.643mm</t>
-  </si>
-  <si>
-    <t>-65.063mm</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>CL10A106MQ8NNNC</t>
-  </si>
-  <si>
-    <t>21.082mm</t>
-  </si>
-  <si>
-    <t>-44.958mm</t>
-  </si>
-  <si>
-    <t>-44.258mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>RVT1E101M0607</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.2-R-RD</t>
-  </si>
-  <si>
-    <t>5.207mm</t>
-  </si>
-  <si>
-    <t>-72.771mm</t>
-  </si>
-  <si>
-    <t>2.652mm</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>DS1021-1x2SF11-B</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>11.142mm</t>
-  </si>
-  <si>
-    <t>-64.955mm</t>
-  </si>
-  <si>
-    <t>-63.685mm</t>
-  </si>
-  <si>
-    <t>U15</t>
-  </si>
-  <si>
-    <t>23.749mm</t>
-  </si>
-  <si>
-    <t>-58.547mm</t>
-  </si>
-  <si>
-    <t>22.479mm</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>12.294mm</t>
-  </si>
-  <si>
-    <t>-13.281mm</t>
-  </si>
-  <si>
-    <t>11.024mm</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>4.1mm</t>
-  </si>
-  <si>
-    <t>-28.479mm</t>
-  </si>
-  <si>
-    <t>3.68mm</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>0805W8J0103T5E</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>3.937mm</t>
-  </si>
-  <si>
-    <t>-16.764mm</t>
-  </si>
-  <si>
-    <t>-15.764mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>4*4*1.7 贴片</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-L5.2-W5.2-P3.70-LS6.5</t>
-  </si>
-  <si>
-    <t>4.191mm</t>
-  </si>
-  <si>
-    <t>-23.368mm</t>
-  </si>
-  <si>
-    <t>6.041mm</t>
-  </si>
-  <si>
-    <t>-20.268mm</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>S6125-M2-0.5A</t>
-  </si>
-  <si>
-    <t>FUSE-SMD_L6.1-W2.5</t>
-  </si>
-  <si>
-    <t>88.9mm</t>
-  </si>
-  <si>
-    <t>-73.152mm</t>
-  </si>
-  <si>
-    <t>87.132mm</t>
-  </si>
-  <si>
-    <t>-71.384mm</t>
-  </si>
-  <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>10D471K_C8760</t>
-  </si>
-  <si>
-    <t>RES-TH_L12.5-W6.7-P7.50-D1.2</t>
-  </si>
-  <si>
-    <t>86.995mm</t>
-  </si>
-  <si>
-    <t>-82.423mm</t>
-  </si>
-  <si>
-    <t>83.374mm</t>
-  </si>
-  <si>
-    <t>-81.453mm</t>
-  </si>
-  <si>
-    <t>190pF@1kHz</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>CBG321609U600T</t>
-  </si>
-  <si>
-    <t>L1206</t>
-  </si>
-  <si>
-    <t>22.86mm</t>
-  </si>
-  <si>
-    <t>-53.721mm</t>
-  </si>
-  <si>
-    <t>23.986mm</t>
-  </si>
-  <si>
-    <t>-52.595mm</t>
-  </si>
-  <si>
-    <t>zdc</t>
-  </si>
-  <si>
-    <t>29.591mm</t>
-  </si>
-  <si>
-    <t>-53.975mm</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>WJ124-3.81-04P-14-00A</t>
-  </si>
-  <si>
-    <t>CONN-TH_4P-P3.81_KF124-3.81-4P</t>
-  </si>
-  <si>
-    <t>93.599mm</t>
-  </si>
-  <si>
-    <t>-20.955mm</t>
-  </si>
-  <si>
-    <t>-15.24mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>KT-0603Y</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD</t>
-  </si>
-  <si>
-    <t>29.905mm</t>
-  </si>
-  <si>
-    <t>-31.518mm</t>
-  </si>
-  <si>
-    <t>29.154mm</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>-28.347mm</t>
-  </si>
-  <si>
-    <t>LED3</t>
-  </si>
-  <si>
-    <t>-25.176mm</t>
-  </si>
-  <si>
-    <t>LED4</t>
-  </si>
-  <si>
-    <t>-22.005mm</t>
-  </si>
-  <si>
-    <t>LED5</t>
-  </si>
-  <si>
-    <t>-18.834mm</t>
-  </si>
-  <si>
-    <t>R35</t>
-  </si>
-  <si>
-    <t>0402WGF1401TCE</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>27.322mm</t>
-  </si>
-  <si>
-    <t>-18.961mm</t>
-  </si>
-  <si>
-    <t>27.755mm</t>
-  </si>
-  <si>
-    <t>1.4kΩ</t>
-  </si>
-  <si>
-    <t>R34</t>
-  </si>
-  <si>
-    <t>-22.134mm</t>
-  </si>
-  <si>
-    <t>R33</t>
-  </si>
-  <si>
-    <t>27.449mm</t>
-  </si>
-  <si>
-    <t>-25.308mm</t>
-  </si>
-  <si>
-    <t>27.882mm</t>
-  </si>
-  <si>
-    <t>R32</t>
-  </si>
-  <si>
-    <t>27.195mm</t>
-  </si>
-  <si>
-    <t>-28.355mm</t>
-  </si>
-  <si>
-    <t>27.628mm</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
-    <t>-31.528mm</t>
-  </si>
-  <si>
-    <t>R36</t>
-  </si>
-  <si>
-    <t>0805W8F2200T5E</t>
-  </si>
-  <si>
-    <t>36.14mm</t>
-  </si>
-  <si>
-    <t>-11.378mm</t>
-  </si>
-  <si>
-    <t>35.14mm</t>
-  </si>
-  <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R37</t>
-  </si>
-  <si>
-    <t>36.013mm</t>
-  </si>
-  <si>
-    <t>-25.168mm</t>
-  </si>
-  <si>
-    <t>35.013mm</t>
-  </si>
-  <si>
-    <t>R38</t>
-  </si>
-  <si>
-    <t>-39.084mm</t>
-  </si>
-  <si>
-    <t>R39</t>
-  </si>
-  <si>
-    <t>36.267mm</t>
-  </si>
-  <si>
-    <t>-53.509mm</t>
-  </si>
-  <si>
-    <t>35.267mm</t>
-  </si>
-  <si>
-    <t>R40</t>
-  </si>
-  <si>
-    <t>38.354mm</t>
-  </si>
-  <si>
-    <t>-65.405mm</t>
-  </si>
-  <si>
-    <t>-64.405mm</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>1210W2F4702T5E</t>
-  </si>
-  <si>
-    <t>R1210</t>
-  </si>
-  <si>
-    <t>66.167mm</t>
-  </si>
-  <si>
-    <t>-84.455mm</t>
-  </si>
-  <si>
-    <t>65.148mm</t>
-  </si>
-  <si>
-    <t>-83.436mm</t>
-  </si>
-  <si>
-    <t>47kΩ</t>
-  </si>
-  <si>
-    <t>R42</t>
-  </si>
-  <si>
-    <t>KNP03SJ0100A10</t>
-  </si>
-  <si>
-    <t>RES-TH_BD5.0-L15.5-P19.50-D0.7</t>
-  </si>
-  <si>
-    <t>79.121mm</t>
-  </si>
-  <si>
-    <t>-91.821mm</t>
-  </si>
-  <si>
-    <t>69.703mm</t>
-  </si>
-  <si>
-    <t>-94.344mm</t>
-  </si>
-  <si>
-    <t>10Ω</t>
-  </si>
-  <si>
-    <t>R43</t>
-  </si>
-  <si>
-    <t>61.468mm</t>
-  </si>
-  <si>
-    <t>-89.154mm</t>
-  </si>
-  <si>
-    <t>62.909mm</t>
-  </si>
-  <si>
-    <t>R44</t>
-  </si>
-  <si>
-    <t>MMB02070C4700FB200</t>
-  </si>
-  <si>
-    <t>R0207</t>
-  </si>
-  <si>
-    <t>52.07mm</t>
-  </si>
-  <si>
-    <t>-20.32mm</t>
-  </si>
-  <si>
-    <t>49.62mm</t>
-  </si>
-  <si>
-    <t>470Ω</t>
-  </si>
-  <si>
-    <t>R45</t>
-  </si>
-  <si>
-    <t>52.451mm</t>
-  </si>
-  <si>
     <t>50.001mm</t>
   </si>
   <si>
@@ -1142,6 +1142,150 @@
   </si>
   <si>
     <t>-89.861mm</t>
+  </si>
+  <si>
+    <t>C14.2</t>
+  </si>
+  <si>
+    <t>7.751mm</t>
+  </si>
+  <si>
+    <t>-17.145mm</t>
+  </si>
+  <si>
+    <t>8.451mm</t>
+  </si>
+  <si>
+    <t>R0</t>
+  </si>
+  <si>
+    <t>-10.668mm</t>
+  </si>
+  <si>
+    <t>-11.101mm</t>
+  </si>
+  <si>
+    <t>LED6</t>
+  </si>
+  <si>
+    <t>8.509mm</t>
+  </si>
+  <si>
+    <t>-9.906mm</t>
+  </si>
+  <si>
+    <t>7.758mm</t>
+  </si>
+  <si>
+    <t>LED7</t>
+  </si>
+  <si>
+    <t>24.638mm</t>
+  </si>
+  <si>
+    <t>-50.165mm</t>
+  </si>
+  <si>
+    <t>25.389mm</t>
+  </si>
+  <si>
+    <t>R21.2</t>
+  </si>
+  <si>
+    <t>22.225mm</t>
+  </si>
+  <si>
+    <t>-48.006mm</t>
+  </si>
+  <si>
+    <t>23.704mm</t>
+  </si>
+  <si>
+    <t>U25</t>
+  </si>
+  <si>
+    <t>BLE-SER-A-ANT</t>
+  </si>
+  <si>
+    <t>custom SMD</t>
+  </si>
+  <si>
+    <t>36.469mm</t>
+  </si>
+  <si>
+    <t>-8.255mm</t>
+  </si>
+  <si>
+    <t>31.369mm</t>
+  </si>
+  <si>
+    <t>-10.16mm</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+  <si>
+    <t>21.61mm</t>
+  </si>
+  <si>
+    <t>-8.001mm</t>
+  </si>
+  <si>
+    <t>16.51mm</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>0402WGF1003TCE</t>
+  </si>
+  <si>
+    <t>9.271mm</t>
+  </si>
+  <si>
+    <t>-50.673mm</t>
+  </si>
+  <si>
+    <t>-50.24mm</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>-53.034mm</t>
+  </si>
+  <si>
+    <t>-52.601mm</t>
+  </si>
+  <si>
+    <t>R51</t>
+  </si>
+  <si>
+    <t>-55.455mm</t>
+  </si>
+  <si>
+    <t>-55.022mm</t>
+  </si>
+  <si>
+    <t>R52</t>
+  </si>
+  <si>
+    <t>-58.166mm</t>
+  </si>
+  <si>
+    <t>-57.733mm</t>
+  </si>
+  <si>
+    <t>R53</t>
+  </si>
+  <si>
+    <t>-59.436mm</t>
+  </si>
+  <si>
+    <t>-59.003mm</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -2603,11 +2747,11 @@
         <v>150</v>
       </c>
       <c r="H25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" t="s">
         <v>151</v>
       </c>
-      <c r="I25" t="s">
-        <v>150</v>
-      </c>
       <c r="J25">
         <v>2</v>
       </c>
@@ -2615,7 +2759,7 @@
         <v>20</v>
       </c>
       <c r="L25">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s">
         <v>35</v>
@@ -2726,19 +2870,19 @@
         <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F28" t="s">
         <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
         <v>163</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -2753,36 +2897,36 @@
         <v>35</v>
       </c>
       <c r="N28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s">
         <v>167</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>168</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>169</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>170</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>169</v>
+      </c>
+      <c r="G29" t="s">
+        <v>170</v>
+      </c>
+      <c r="H29" t="s">
         <v>171</v>
       </c>
-      <c r="F29" t="s">
+      <c r="I29" t="s">
         <v>170</v>
-      </c>
-      <c r="G29" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" t="s">
-        <v>172</v>
-      </c>
-      <c r="I29" t="s">
-        <v>171</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -2797,36 +2941,36 @@
         <v>35</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" t="s">
         <v>174</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>175</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>176</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>177</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" t="s">
         <v>178</v>
-      </c>
-      <c r="F30" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" t="s">
-        <v>177</v>
-      </c>
-      <c r="I30" t="s">
-        <v>179</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2841,36 +2985,36 @@
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" t="s">
         <v>180</v>
       </c>
-      <c r="B31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" t="s">
-        <v>176</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>181</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>180</v>
+      </c>
+      <c r="G31" t="s">
+        <v>181</v>
+      </c>
+      <c r="H31" t="s">
         <v>182</v>
       </c>
-      <c r="F31" t="s">
+      <c r="I31" t="s">
         <v>181</v>
-      </c>
-      <c r="G31" t="s">
-        <v>182</v>
-      </c>
-      <c r="H31" t="s">
-        <v>183</v>
-      </c>
-      <c r="I31" t="s">
-        <v>182</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2885,36 +3029,36 @@
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" t="s">
         <v>184</v>
       </c>
-      <c r="B32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C32" t="s">
-        <v>176</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>185</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" t="s">
+        <v>185</v>
+      </c>
+      <c r="H32" t="s">
         <v>186</v>
       </c>
-      <c r="F32" t="s">
+      <c r="I32" t="s">
         <v>185</v>
-      </c>
-      <c r="G32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I32" t="s">
-        <v>186</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -2929,12 +3073,12 @@
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
         <v>138</v>
@@ -2943,22 +3087,22 @@
         <v>139</v>
       </c>
       <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
         <v>189</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>188</v>
+      </c>
+      <c r="G33" t="s">
+        <v>189</v>
+      </c>
+      <c r="H33" t="s">
         <v>190</v>
       </c>
-      <c r="F33" t="s">
+      <c r="I33" t="s">
         <v>189</v>
-      </c>
-      <c r="G33" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" t="s">
-        <v>190</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2978,31 +3122,31 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>191</v>
+      </c>
+      <c r="B34" t="s">
         <v>192</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>193</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>194</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>195</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G34" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" t="s">
+        <v>194</v>
+      </c>
+      <c r="I34" t="s">
         <v>196</v>
-      </c>
-      <c r="F34" t="s">
-        <v>195</v>
-      </c>
-      <c r="G34" t="s">
-        <v>196</v>
-      </c>
-      <c r="H34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" t="s">
-        <v>197</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -3017,36 +3161,36 @@
         <v>35</v>
       </c>
       <c r="N34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B35" t="s">
         <v>199</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>200</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>201</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>202</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>201</v>
+      </c>
+      <c r="G35" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" t="s">
         <v>203</v>
       </c>
-      <c r="F35" t="s">
-        <v>202</v>
-      </c>
-      <c r="G35" t="s">
-        <v>203</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>204</v>
-      </c>
-      <c r="I35" t="s">
-        <v>205</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -3061,36 +3205,36 @@
         <v>35</v>
       </c>
       <c r="N35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
         <v>206</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>207</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>208</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>209</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>208</v>
+      </c>
+      <c r="G36" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" t="s">
         <v>210</v>
       </c>
-      <c r="F36" t="s">
-        <v>209</v>
-      </c>
-      <c r="G36" t="s">
-        <v>210</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>211</v>
-      </c>
-      <c r="I36" t="s">
-        <v>212</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -3105,36 +3249,36 @@
         <v>35</v>
       </c>
       <c r="N36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" t="s">
         <v>213</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>214</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>215</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>216</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H37" t="s">
         <v>217</v>
       </c>
-      <c r="F37" t="s">
-        <v>216</v>
-      </c>
-      <c r="G37" t="s">
-        <v>217</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>218</v>
-      </c>
-      <c r="I37" t="s">
-        <v>219</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -3149,36 +3293,36 @@
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" t="s">
         <v>221</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>222</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>223</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>224</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
+        <v>223</v>
+      </c>
+      <c r="G38" t="s">
+        <v>224</v>
+      </c>
+      <c r="H38" t="s">
         <v>225</v>
       </c>
-      <c r="F38" t="s">
-        <v>224</v>
-      </c>
-      <c r="G38" t="s">
-        <v>225</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>226</v>
-      </c>
-      <c r="I38" t="s">
-        <v>227</v>
       </c>
       <c r="J38">
         <v>2</v>
@@ -3193,12 +3337,12 @@
         <v>35</v>
       </c>
       <c r="N38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B39" t="s">
         <v>133</v>
@@ -3207,22 +3351,22 @@
         <v>134</v>
       </c>
       <c r="D39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E39" t="s">
         <v>229</v>
       </c>
-      <c r="E39" t="s">
-        <v>230</v>
-      </c>
       <c r="F39" t="s">
+        <v>228</v>
+      </c>
+      <c r="G39" t="s">
         <v>229</v>
       </c>
-      <c r="G39" t="s">
-        <v>230</v>
-      </c>
       <c r="H39" t="s">
+        <v>228</v>
+      </c>
+      <c r="I39" t="s">
         <v>229</v>
-      </c>
-      <c r="I39" t="s">
-        <v>230</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -3242,31 +3386,31 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" t="s">
         <v>231</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>232</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>233</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>234</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" t="s">
+        <v>234</v>
+      </c>
+      <c r="H40" t="s">
+        <v>233</v>
+      </c>
+      <c r="I40" t="s">
         <v>235</v>
-      </c>
-      <c r="F40" t="s">
-        <v>234</v>
-      </c>
-      <c r="G40" t="s">
-        <v>235</v>
-      </c>
-      <c r="H40" t="s">
-        <v>234</v>
-      </c>
-      <c r="I40" t="s">
-        <v>236</v>
       </c>
       <c r="J40">
         <v>4</v>
@@ -3281,36 +3425,36 @@
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" t="s">
         <v>237</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>238</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>239</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>240</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" t="s">
+        <v>240</v>
+      </c>
+      <c r="H41" t="s">
         <v>241</v>
       </c>
-      <c r="F41" t="s">
+      <c r="I41" t="s">
         <v>240</v>
-      </c>
-      <c r="G41" t="s">
-        <v>241</v>
-      </c>
-      <c r="H41" t="s">
-        <v>242</v>
-      </c>
-      <c r="I41" t="s">
-        <v>241</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -3325,36 +3469,36 @@
         <v>35</v>
       </c>
       <c r="N41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" t="s">
+        <v>238</v>
+      </c>
+      <c r="D42" t="s">
+        <v>239</v>
+      </c>
+      <c r="E42" t="s">
         <v>243</v>
       </c>
-      <c r="B42" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>239</v>
       </c>
-      <c r="D42" t="s">
-        <v>240</v>
-      </c>
-      <c r="E42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F42" t="s">
-        <v>240</v>
-      </c>
       <c r="G42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -3369,36 +3513,36 @@
         <v>35</v>
       </c>
       <c r="N42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C43" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" t="s">
         <v>245</v>
       </c>
-      <c r="B43" t="s">
-        <v>238</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
         <v>239</v>
       </c>
-      <c r="D43" t="s">
-        <v>240</v>
-      </c>
-      <c r="E43" t="s">
-        <v>246</v>
-      </c>
-      <c r="F43" t="s">
-        <v>240</v>
-      </c>
       <c r="G43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J43">
         <v>2</v>
@@ -3413,36 +3557,36 @@
         <v>35</v>
       </c>
       <c r="N43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" t="s">
+        <v>237</v>
+      </c>
+      <c r="C44" t="s">
+        <v>238</v>
+      </c>
+      <c r="D44" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" t="s">
         <v>247</v>
       </c>
-      <c r="B44" t="s">
-        <v>238</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="F44" t="s">
         <v>239</v>
       </c>
-      <c r="D44" t="s">
-        <v>240</v>
-      </c>
-      <c r="E44" t="s">
-        <v>248</v>
-      </c>
-      <c r="F44" t="s">
-        <v>240</v>
-      </c>
       <c r="G44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3457,36 +3601,36 @@
         <v>35</v>
       </c>
       <c r="N44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>248</v>
+      </c>
+      <c r="B45" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" t="s">
         <v>249</v>
       </c>
-      <c r="B45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>239</v>
       </c>
-      <c r="D45" t="s">
-        <v>240</v>
-      </c>
-      <c r="E45" t="s">
-        <v>250</v>
-      </c>
-      <c r="F45" t="s">
-        <v>240</v>
-      </c>
       <c r="G45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -3501,36 +3645,36 @@
         <v>35</v>
       </c>
       <c r="N45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>250</v>
+      </c>
+      <c r="B46" t="s">
         <v>251</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>252</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>253</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>254</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
+        <v>253</v>
+      </c>
+      <c r="G46" t="s">
+        <v>254</v>
+      </c>
+      <c r="H46" t="s">
         <v>255</v>
       </c>
-      <c r="F46" t="s">
+      <c r="I46" t="s">
         <v>254</v>
-      </c>
-      <c r="G46" t="s">
-        <v>255</v>
-      </c>
-      <c r="H46" t="s">
-        <v>256</v>
-      </c>
-      <c r="I46" t="s">
-        <v>255</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -3545,36 +3689,36 @@
         <v>35</v>
       </c>
       <c r="N46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>257</v>
+      </c>
+      <c r="B47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C47" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
         <v>258</v>
       </c>
-      <c r="B47" t="s">
-        <v>252</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="F47" t="s">
         <v>253</v>
       </c>
-      <c r="D47" t="s">
-        <v>254</v>
-      </c>
-      <c r="E47" t="s">
-        <v>259</v>
-      </c>
-      <c r="F47" t="s">
-        <v>254</v>
-      </c>
       <c r="G47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3589,36 +3733,36 @@
         <v>35</v>
       </c>
       <c r="N47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48" t="s">
         <v>260</v>
       </c>
-      <c r="B48" t="s">
-        <v>252</v>
-      </c>
-      <c r="C48" t="s">
-        <v>253</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>261</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
+        <v>260</v>
+      </c>
+      <c r="G48" t="s">
+        <v>261</v>
+      </c>
+      <c r="H48" t="s">
         <v>262</v>
       </c>
-      <c r="F48" t="s">
+      <c r="I48" t="s">
         <v>261</v>
-      </c>
-      <c r="G48" t="s">
-        <v>262</v>
-      </c>
-      <c r="H48" t="s">
-        <v>263</v>
-      </c>
-      <c r="I48" t="s">
-        <v>262</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3633,36 +3777,36 @@
         <v>35</v>
       </c>
       <c r="N48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" t="s">
         <v>264</v>
       </c>
-      <c r="B49" t="s">
-        <v>252</v>
-      </c>
-      <c r="C49" t="s">
-        <v>253</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>265</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>264</v>
+      </c>
+      <c r="G49" t="s">
+        <v>265</v>
+      </c>
+      <c r="H49" t="s">
         <v>266</v>
       </c>
-      <c r="F49" t="s">
+      <c r="I49" t="s">
         <v>265</v>
-      </c>
-      <c r="G49" t="s">
-        <v>266</v>
-      </c>
-      <c r="H49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I49" t="s">
-        <v>266</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -3677,36 +3821,36 @@
         <v>35</v>
       </c>
       <c r="N49" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" t="s">
+        <v>252</v>
+      </c>
+      <c r="D50" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" t="s">
         <v>268</v>
       </c>
-      <c r="B50" t="s">
-        <v>252</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
         <v>253</v>
       </c>
-      <c r="D50" t="s">
-        <v>254</v>
-      </c>
-      <c r="E50" t="s">
-        <v>269</v>
-      </c>
-      <c r="F50" t="s">
-        <v>254</v>
-      </c>
       <c r="G50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -3721,36 +3865,36 @@
         <v>35</v>
       </c>
       <c r="N50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" t="s">
         <v>270</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>193</v>
+      </c>
+      <c r="D51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" t="s">
-        <v>194</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>272</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
+        <v>271</v>
+      </c>
+      <c r="G51" t="s">
+        <v>272</v>
+      </c>
+      <c r="H51" t="s">
         <v>273</v>
       </c>
-      <c r="F51" t="s">
+      <c r="I51" t="s">
         <v>272</v>
-      </c>
-      <c r="G51" t="s">
-        <v>273</v>
-      </c>
-      <c r="H51" t="s">
-        <v>274</v>
-      </c>
-      <c r="I51" t="s">
-        <v>273</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -3765,36 +3909,36 @@
         <v>35</v>
       </c>
       <c r="N51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>275</v>
+      </c>
+      <c r="B52" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" t="s">
+        <v>193</v>
+      </c>
+      <c r="D52" t="s">
         <v>276</v>
       </c>
-      <c r="B52" t="s">
-        <v>271</v>
-      </c>
-      <c r="C52" t="s">
-        <v>194</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>277</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>276</v>
+      </c>
+      <c r="G52" t="s">
+        <v>277</v>
+      </c>
+      <c r="H52" t="s">
         <v>278</v>
       </c>
-      <c r="F52" t="s">
+      <c r="I52" t="s">
         <v>277</v>
-      </c>
-      <c r="G52" t="s">
-        <v>278</v>
-      </c>
-      <c r="H52" t="s">
-        <v>279</v>
-      </c>
-      <c r="I52" t="s">
-        <v>278</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3809,36 +3953,36 @@
         <v>35</v>
       </c>
       <c r="N52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>279</v>
+      </c>
+      <c r="B53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" t="s">
+        <v>276</v>
+      </c>
+      <c r="E53" t="s">
         <v>280</v>
       </c>
-      <c r="B53" t="s">
-        <v>271</v>
-      </c>
-      <c r="C53" t="s">
-        <v>194</v>
-      </c>
-      <c r="D53" t="s">
-        <v>277</v>
-      </c>
-      <c r="E53" t="s">
-        <v>281</v>
-      </c>
       <c r="F53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G53" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H53" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I53" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3853,36 +3997,36 @@
         <v>35</v>
       </c>
       <c r="N53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>281</v>
+      </c>
+      <c r="B54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" t="s">
         <v>282</v>
       </c>
-      <c r="B54" t="s">
-        <v>271</v>
-      </c>
-      <c r="C54" t="s">
-        <v>194</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>283</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" t="s">
+        <v>283</v>
+      </c>
+      <c r="H54" t="s">
         <v>284</v>
       </c>
-      <c r="F54" t="s">
+      <c r="I54" t="s">
         <v>283</v>
-      </c>
-      <c r="G54" t="s">
-        <v>284</v>
-      </c>
-      <c r="H54" t="s">
-        <v>285</v>
-      </c>
-      <c r="I54" t="s">
-        <v>284</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3897,36 +4041,36 @@
         <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>285</v>
+      </c>
+      <c r="B55" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" t="s">
         <v>286</v>
       </c>
-      <c r="B55" t="s">
-        <v>271</v>
-      </c>
-      <c r="C55" t="s">
-        <v>194</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>287</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
+        <v>286</v>
+      </c>
+      <c r="G55" t="s">
+        <v>287</v>
+      </c>
+      <c r="H55" t="s">
+        <v>286</v>
+      </c>
+      <c r="I55" t="s">
         <v>288</v>
-      </c>
-      <c r="F55" t="s">
-        <v>287</v>
-      </c>
-      <c r="G55" t="s">
-        <v>288</v>
-      </c>
-      <c r="H55" t="s">
-        <v>287</v>
-      </c>
-      <c r="I55" t="s">
-        <v>289</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -3941,36 +4085,36 @@
         <v>35</v>
       </c>
       <c r="N55" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>289</v>
+      </c>
+      <c r="B56" t="s">
         <v>290</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>291</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>292</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>293</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>292</v>
+      </c>
+      <c r="G56" t="s">
+        <v>293</v>
+      </c>
+      <c r="H56" t="s">
         <v>294</v>
       </c>
-      <c r="F56" t="s">
-        <v>293</v>
-      </c>
-      <c r="G56" t="s">
-        <v>294</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>295</v>
-      </c>
-      <c r="I56" t="s">
-        <v>296</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3985,36 +4129,36 @@
         <v>35</v>
       </c>
       <c r="N56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>297</v>
+      </c>
+      <c r="B57" t="s">
         <v>298</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>299</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>300</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>301</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
+        <v>300</v>
+      </c>
+      <c r="G57" t="s">
+        <v>301</v>
+      </c>
+      <c r="H57" t="s">
         <v>302</v>
       </c>
-      <c r="F57" t="s">
-        <v>301</v>
-      </c>
-      <c r="G57" t="s">
-        <v>302</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>303</v>
-      </c>
-      <c r="I57" t="s">
-        <v>304</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -4029,36 +4173,36 @@
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>305</v>
+      </c>
+      <c r="B58" t="s">
+        <v>290</v>
+      </c>
+      <c r="C58" t="s">
+        <v>291</v>
+      </c>
+      <c r="D58" t="s">
         <v>306</v>
       </c>
-      <c r="B58" t="s">
-        <v>291</v>
-      </c>
-      <c r="C58" t="s">
-        <v>292</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>307</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
+        <v>306</v>
+      </c>
+      <c r="G58" t="s">
+        <v>307</v>
+      </c>
+      <c r="H58" t="s">
         <v>308</v>
       </c>
-      <c r="F58" t="s">
+      <c r="I58" t="s">
         <v>307</v>
-      </c>
-      <c r="G58" t="s">
-        <v>308</v>
-      </c>
-      <c r="H58" t="s">
-        <v>309</v>
-      </c>
-      <c r="I58" t="s">
-        <v>308</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -4073,36 +4217,36 @@
         <v>35</v>
       </c>
       <c r="N58" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>309</v>
+      </c>
+      <c r="B59" t="s">
         <v>310</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>311</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>312</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>313</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" t="s">
+        <v>313</v>
+      </c>
+      <c r="H59" t="s">
         <v>314</v>
       </c>
-      <c r="F59" t="s">
+      <c r="I59" t="s">
         <v>313</v>
-      </c>
-      <c r="G59" t="s">
-        <v>314</v>
-      </c>
-      <c r="H59" t="s">
-        <v>315</v>
-      </c>
-      <c r="I59" t="s">
-        <v>314</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -4117,36 +4261,36 @@
         <v>35</v>
       </c>
       <c r="N59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>316</v>
+      </c>
+      <c r="B60" t="s">
+        <v>310</v>
+      </c>
+      <c r="C60" t="s">
+        <v>311</v>
+      </c>
+      <c r="D60" t="s">
         <v>317</v>
       </c>
-      <c r="B60" t="s">
-        <v>311</v>
-      </c>
-      <c r="C60" t="s">
-        <v>312</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>318</v>
       </c>
-      <c r="E60" t="s">
-        <v>146</v>
-      </c>
       <c r="F60" t="s">
+        <v>317</v>
+      </c>
+      <c r="G60" t="s">
         <v>318</v>
-      </c>
-      <c r="G60" t="s">
-        <v>146</v>
       </c>
       <c r="H60" t="s">
         <v>319</v>
       </c>
       <c r="I60" t="s">
-        <v>146</v>
+        <v>318</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -4161,7 +4305,7 @@
         <v>35</v>
       </c>
       <c r="N60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -4169,25 +4313,25 @@
         <v>320</v>
       </c>
       <c r="B61" t="s">
+        <v>310</v>
+      </c>
+      <c r="C61" t="s">
         <v>311</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>312</v>
-      </c>
-      <c r="D61" t="s">
-        <v>313</v>
       </c>
       <c r="E61" t="s">
         <v>321</v>
       </c>
       <c r="F61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G61" t="s">
         <v>321</v>
       </c>
       <c r="H61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I61" t="s">
         <v>321</v>
@@ -4205,7 +4349,7 @@
         <v>35</v>
       </c>
       <c r="N61" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -4213,10 +4357,10 @@
         <v>322</v>
       </c>
       <c r="B62" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" t="s">
         <v>311</v>
-      </c>
-      <c r="C62" t="s">
-        <v>312</v>
       </c>
       <c r="D62" t="s">
         <v>323</v>
@@ -4249,7 +4393,7 @@
         <v>35</v>
       </c>
       <c r="N62" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -4257,10 +4401,10 @@
         <v>326</v>
       </c>
       <c r="B63" t="s">
+        <v>310</v>
+      </c>
+      <c r="C63" t="s">
         <v>311</v>
-      </c>
-      <c r="C63" t="s">
-        <v>312</v>
       </c>
       <c r="D63" t="s">
         <v>327</v>
@@ -4293,7 +4437,7 @@
         <v>35</v>
       </c>
       <c r="N63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -4486,13 +4630,13 @@
         <v>333</v>
       </c>
       <c r="E68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F68" t="s">
         <v>333</v>
       </c>
       <c r="G68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H68" t="s">
         <v>335</v>
@@ -4601,7 +4745,7 @@
         <v>35</v>
       </c>
       <c r="N70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -4697,10 +4841,10 @@
         <v>371</v>
       </c>
       <c r="B73" t="s">
+        <v>174</v>
+      </c>
+      <c r="C73" t="s">
         <v>175</v>
-      </c>
-      <c r="C73" t="s">
-        <v>176</v>
       </c>
       <c r="D73" t="s">
         <v>372</v>
@@ -4733,7 +4877,7 @@
         <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -4778,6 +4922,534 @@
       </c>
       <c r="N74" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>377</v>
+      </c>
+      <c r="B75" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" t="s">
+        <v>378</v>
+      </c>
+      <c r="E75" t="s">
+        <v>379</v>
+      </c>
+      <c r="F75" t="s">
+        <v>378</v>
+      </c>
+      <c r="G75" t="s">
+        <v>379</v>
+      </c>
+      <c r="H75" t="s">
+        <v>380</v>
+      </c>
+      <c r="I75" t="s">
+        <v>379</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75" t="s">
+        <v>20</v>
+      </c>
+      <c r="L75">
+        <v>180</v>
+      </c>
+      <c r="M75" t="s">
+        <v>35</v>
+      </c>
+      <c r="N75" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>381</v>
+      </c>
+      <c r="B76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" t="s">
+        <v>252</v>
+      </c>
+      <c r="D76" t="s">
+        <v>372</v>
+      </c>
+      <c r="E76" t="s">
+        <v>382</v>
+      </c>
+      <c r="F76" t="s">
+        <v>372</v>
+      </c>
+      <c r="G76" t="s">
+        <v>382</v>
+      </c>
+      <c r="H76" t="s">
+        <v>372</v>
+      </c>
+      <c r="I76" t="s">
+        <v>383</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>20</v>
+      </c>
+      <c r="L76">
+        <v>90</v>
+      </c>
+      <c r="M76" t="s">
+        <v>35</v>
+      </c>
+      <c r="N76" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>384</v>
+      </c>
+      <c r="B77" t="s">
+        <v>237</v>
+      </c>
+      <c r="C77" t="s">
+        <v>238</v>
+      </c>
+      <c r="D77" t="s">
+        <v>385</v>
+      </c>
+      <c r="E77" t="s">
+        <v>386</v>
+      </c>
+      <c r="F77" t="s">
+        <v>385</v>
+      </c>
+      <c r="G77" t="s">
+        <v>386</v>
+      </c>
+      <c r="H77" t="s">
+        <v>387</v>
+      </c>
+      <c r="I77" t="s">
+        <v>386</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="K77" t="s">
+        <v>20</v>
+      </c>
+      <c r="L77">
+        <v>180</v>
+      </c>
+      <c r="M77" t="s">
+        <v>35</v>
+      </c>
+      <c r="N77" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>388</v>
+      </c>
+      <c r="B78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s">
+        <v>238</v>
+      </c>
+      <c r="D78" t="s">
+        <v>389</v>
+      </c>
+      <c r="E78" t="s">
+        <v>390</v>
+      </c>
+      <c r="F78" t="s">
+        <v>389</v>
+      </c>
+      <c r="G78" t="s">
+        <v>390</v>
+      </c>
+      <c r="H78" t="s">
+        <v>391</v>
+      </c>
+      <c r="I78" t="s">
+        <v>390</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78" t="s">
+        <v>20</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="s">
+        <v>35</v>
+      </c>
+      <c r="N78" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>392</v>
+      </c>
+      <c r="B79" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" t="s">
+        <v>393</v>
+      </c>
+      <c r="E79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F79" t="s">
+        <v>393</v>
+      </c>
+      <c r="G79" t="s">
+        <v>394</v>
+      </c>
+      <c r="H79" t="s">
+        <v>395</v>
+      </c>
+      <c r="I79" t="s">
+        <v>394</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79" t="s">
+        <v>20</v>
+      </c>
+      <c r="L79">
+        <v>180</v>
+      </c>
+      <c r="M79" t="s">
+        <v>35</v>
+      </c>
+      <c r="N79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>396</v>
+      </c>
+      <c r="B80" t="s">
+        <v>397</v>
+      </c>
+      <c r="C80" t="s">
+        <v>398</v>
+      </c>
+      <c r="D80" t="s">
+        <v>399</v>
+      </c>
+      <c r="E80" t="s">
+        <v>400</v>
+      </c>
+      <c r="F80" t="s">
+        <v>401</v>
+      </c>
+      <c r="G80" t="s">
+        <v>400</v>
+      </c>
+      <c r="H80" t="s">
+        <v>399</v>
+      </c>
+      <c r="I80" t="s">
+        <v>402</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>20</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
+        <v>35</v>
+      </c>
+      <c r="N80" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>403</v>
+      </c>
+      <c r="B81" t="s">
+        <v>397</v>
+      </c>
+      <c r="C81" t="s">
+        <v>398</v>
+      </c>
+      <c r="D81" t="s">
+        <v>404</v>
+      </c>
+      <c r="E81" t="s">
+        <v>405</v>
+      </c>
+      <c r="F81" t="s">
+        <v>406</v>
+      </c>
+      <c r="G81" t="s">
+        <v>405</v>
+      </c>
+      <c r="H81" t="s">
+        <v>404</v>
+      </c>
+      <c r="I81" t="s">
+        <v>386</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="s">
+        <v>35</v>
+      </c>
+      <c r="N81" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>407</v>
+      </c>
+      <c r="B82" t="s">
+        <v>408</v>
+      </c>
+      <c r="C82" t="s">
+        <v>252</v>
+      </c>
+      <c r="D82" t="s">
+        <v>409</v>
+      </c>
+      <c r="E82" t="s">
+        <v>410</v>
+      </c>
+      <c r="F82" t="s">
+        <v>409</v>
+      </c>
+      <c r="G82" t="s">
+        <v>410</v>
+      </c>
+      <c r="H82" t="s">
+        <v>409</v>
+      </c>
+      <c r="I82" t="s">
+        <v>411</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82">
+        <v>270</v>
+      </c>
+      <c r="M82" t="s">
+        <v>35</v>
+      </c>
+      <c r="N82" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>413</v>
+      </c>
+      <c r="B83" t="s">
+        <v>408</v>
+      </c>
+      <c r="C83" t="s">
+        <v>252</v>
+      </c>
+      <c r="D83" t="s">
+        <v>409</v>
+      </c>
+      <c r="E83" t="s">
+        <v>414</v>
+      </c>
+      <c r="F83" t="s">
+        <v>409</v>
+      </c>
+      <c r="G83" t="s">
+        <v>414</v>
+      </c>
+      <c r="H83" t="s">
+        <v>409</v>
+      </c>
+      <c r="I83" t="s">
+        <v>415</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83">
+        <v>270</v>
+      </c>
+      <c r="M83" t="s">
+        <v>35</v>
+      </c>
+      <c r="N83" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>416</v>
+      </c>
+      <c r="B84" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" t="s">
+        <v>252</v>
+      </c>
+      <c r="D84" t="s">
+        <v>409</v>
+      </c>
+      <c r="E84" t="s">
+        <v>417</v>
+      </c>
+      <c r="F84" t="s">
+        <v>409</v>
+      </c>
+      <c r="G84" t="s">
+        <v>417</v>
+      </c>
+      <c r="H84" t="s">
+        <v>409</v>
+      </c>
+      <c r="I84" t="s">
+        <v>418</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84">
+        <v>270</v>
+      </c>
+      <c r="M84" t="s">
+        <v>35</v>
+      </c>
+      <c r="N84" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>419</v>
+      </c>
+      <c r="B85" t="s">
+        <v>408</v>
+      </c>
+      <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
+        <v>409</v>
+      </c>
+      <c r="E85" t="s">
+        <v>420</v>
+      </c>
+      <c r="F85" t="s">
+        <v>409</v>
+      </c>
+      <c r="G85" t="s">
+        <v>420</v>
+      </c>
+      <c r="H85" t="s">
+        <v>409</v>
+      </c>
+      <c r="I85" t="s">
+        <v>421</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85" t="s">
+        <v>20</v>
+      </c>
+      <c r="L85">
+        <v>270</v>
+      </c>
+      <c r="M85" t="s">
+        <v>35</v>
+      </c>
+      <c r="N85" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>422</v>
+      </c>
+      <c r="B86" t="s">
+        <v>408</v>
+      </c>
+      <c r="C86" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" t="s">
+        <v>375</v>
+      </c>
+      <c r="E86" t="s">
+        <v>423</v>
+      </c>
+      <c r="F86" t="s">
+        <v>375</v>
+      </c>
+      <c r="G86" t="s">
+        <v>423</v>
+      </c>
+      <c r="H86" t="s">
+        <v>375</v>
+      </c>
+      <c r="I86" t="s">
+        <v>424</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86" t="s">
+        <v>20</v>
+      </c>
+      <c r="L86">
+        <v>270</v>
+      </c>
+      <c r="M86" t="s">
+        <v>35</v>
+      </c>
+      <c r="N86" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
